--- a/data-preprocessing/rpc-footprints/1 - Crops/Field operations.xlsx
+++ b/data-preprocessing/rpc-footprints/1 - Crops/Field operations.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr filterPrivacy="1" updateLinks="never" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C04F6B-F4EA-7C45-9FDF-6D65E9F15C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA945E1-0724-014C-8E51-1DAA729866E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5200" yWindow="660" windowWidth="14400" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5200" yWindow="660" windowWidth="24200" windowHeight="14040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INFO" sheetId="117" r:id="rId1"/>
@@ -2451,7 +2451,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2488,6 +2488,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2512,7 +2518,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2596,6 +2602,9 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7599,20 +7608,20 @@
         <v>675</v>
       </c>
     </row>
-    <row r="27" spans="1:87" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:87" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="43" t="s">
         <v>312</v>
       </c>
-      <c r="CI27" t="s">
+      <c r="CI27" s="44" t="s">
         <v>707</v>
       </c>
     </row>
@@ -7701,50 +7710,50 @@
         <v>675</v>
       </c>
     </row>
-    <row r="34" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:199" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="43" t="s">
         <v>146</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="43" t="s">
         <v>687</v>
       </c>
-      <c r="AU34" s="12"/>
-      <c r="AZ34" t="s">
+      <c r="AU34" s="45"/>
+      <c r="AZ34" s="44" t="s">
         <v>685</v>
       </c>
-      <c r="BX34" t="s">
+      <c r="BX34" s="44" t="s">
         <v>686</v>
       </c>
-      <c r="CJ34" t="s">
+      <c r="CJ34" s="44" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="35" spans="1:199" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:199" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="44" t="s">
         <v>688</v>
       </c>
-      <c r="CI35" t="s">
+      <c r="CI35" s="44" t="s">
         <v>689</v>
       </c>
-      <c r="CJ35" t="s">
+      <c r="CJ35" s="44" t="s">
         <v>689</v>
       </c>
-      <c r="EO35" t="s">
+      <c r="EO35" s="44" t="s">
         <v>689</v>
       </c>
     </row>
@@ -8082,20 +8091,20 @@
         <v>676</v>
       </c>
     </row>
-    <row r="59" spans="1:87" x14ac:dyDescent="0.2">
-      <c r="A59" s="2" t="s">
+    <row r="59" spans="1:87" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="43" t="s">
         <v>173</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" s="43" t="s">
         <v>312</v>
       </c>
-      <c r="CI59" t="s">
+      <c r="CI59" s="44" t="s">
         <v>708</v>
       </c>
     </row>
@@ -9101,20 +9110,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="20b5f8f8-e964-4ea5-9bc5-5fa83731a92f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="20b5f8f8-e964-4ea5-9bc5-5fa83731a92f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9353,19 +9362,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A16A6EDB-4C6A-433C-9B54-BF88B9AEEE87}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{627ED23C-5EEB-4F10-AA20-79B788D8342E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="20b5f8f8-e964-4ea5-9bc5-5fa83731a92f"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{627ED23C-5EEB-4F10-AA20-79B788D8342E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A16A6EDB-4C6A-433C-9B54-BF88B9AEEE87}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="20b5f8f8-e964-4ea5-9bc5-5fa83731a92f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
